--- a/output/pdf_financials_xlsx/ECR.xlsx
+++ b/output/pdf_financials_xlsx/ECR.xlsx
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035725</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026812</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -1008,31 +1008,31 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007820000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09914100000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.164374</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.112325</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.038575</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.10954</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.140583</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.099064</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.162395</v>
       </c>
     </row>
     <row r="13">
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.614618</v>
+        <v>-1.578893</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.128946</v>
+        <v>-2.102134</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.692613</v>
+        <v>-0.684793</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.866844</v>
+        <v>-1.767703</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.989092</v>
+        <v>-4.824718</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.984863</v>
+        <v>-0.872538</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.342945</v>
+        <v>-0.30437</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-1.092355</v>
+        <v>-0.982815</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.387911</v>
+        <v>-1.247328</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-10.141714</v>
+        <v>-10.04265</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.339054</v>
+        <v>-4.176659</v>
       </c>
     </row>
     <row r="28">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.614618</v>
+        <v>-1.578893</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.128946</v>
+        <v>-2.102134</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1999,31 +1999,31 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.692613</v>
+        <v>-0.684793</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.866844</v>
+        <v>-1.767703</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.989092</v>
+        <v>-4.824718</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.984863</v>
+        <v>-0.872538</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.342945</v>
+        <v>-0.30437</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-1.092355</v>
+        <v>-0.982815</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.387911</v>
+        <v>-1.247328</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.141714</v>
+        <v>-10.04265</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.339054</v>
+        <v>-4.176659</v>
       </c>
     </row>
     <row r="30">
@@ -2285,10 +2285,10 @@
         <v>4.739698</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.228177</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.749672</v>
       </c>
     </row>
     <row r="35">
@@ -2383,10 +2383,10 @@
         <v>4.739698</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.228177</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>7.749672</v>
       </c>
     </row>
     <row r="37">
@@ -2971,10 +2971,10 @@
         <v>0.151291</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.394244</v>
+        <v>0.166067</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>8.011333</v>
+        <v>0.261661</v>
       </c>
     </row>
     <row r="49">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -31292,7 +31292,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">

--- a/output/pdf_financials_xlsx/ECR.xlsx
+++ b/output/pdf_financials_xlsx/ECR.xlsx
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.004643</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.007484</v>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.003169</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -1953,22 +1953,22 @@
         <v>0</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.007867000000000001</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.020328</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.023564</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.022739</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.02434</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.026313</v>
       </c>
     </row>
     <row r="29">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.578893</v>
+        <v>-1.57425</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.102134</v>
+        <v>-2.09465</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.684793</v>
+        <v>-0.681624</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-1.767703</v>
@@ -2008,22 +2008,22 @@
         <v>-4.824718</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.872538</v>
+        <v>-0.864671</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.30437</v>
+        <v>-0.284042</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.982815</v>
+        <v>-0.959251</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.247328</v>
+        <v>-1.224589</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-10.04265</v>
+        <v>-10.01831</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.176659</v>
+        <v>-4.150346</v>
       </c>
     </row>
     <row r="30">
@@ -5519,13 +5519,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.000589</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.004643</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.007484</v>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.003169</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -5547,22 +5547,22 @@
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.007867000000000001</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.020328</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.023564</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.022739</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.02434</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.026313</v>
       </c>
     </row>
     <row r="101">
@@ -21112,7 +21112,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="n">
         <v>0.000589</v>
       </c>
@@ -21182,7 +21186,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24390,7 +24398,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -24474,7 +24486,11 @@
           <t>Depreciation of right-of-use assets (note 8)</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -30242,7 +30258,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -30314,7 +30334,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ECR.xlsx
+++ b/output/pdf_financials_xlsx/ECR.xlsx
@@ -557,15 +557,11 @@
       <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -612,15 +608,11 @@
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -667,15 +659,11 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -717,20 +705,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.026388</v>
+        <v>0.073335</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.029641</v>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.062309</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.0542</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.02267</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.043308</v>
@@ -777,15 +761,11 @@
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -832,15 +812,11 @@
       <c r="D9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -887,15 +863,11 @@
       <c r="D10" s="3" t="n">
         <v>1.102966</v>
       </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E10" s="3" t="n">
+        <v>0.867586</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.803491</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.861418</v>
@@ -942,15 +914,11 @@
       <c r="D11" s="3" t="n">
         <v>-1.102966</v>
       </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E11" s="3" t="n">
+        <v>-0.867586</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>-0.803491</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>-0.861418</v>
@@ -997,15 +965,11 @@
       <c r="D12" s="3" t="n">
         <v>-0.026812</v>
       </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="3" t="n">
+        <v>-0.014317</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>-0.008411</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>-0.007820000000000001</v>
@@ -1052,15 +1016,11 @@
       <c r="D13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1107,15 +1067,11 @@
       <c r="D14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1162,15 +1118,11 @@
       <c r="D15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1217,15 +1169,11 @@
       <c r="D16" s="3" t="n">
         <v>-2.128946</v>
       </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="3" t="n">
+        <v>-1.427049</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-2.037757</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-0.692613</v>
@@ -1272,15 +1220,11 @@
       <c r="D17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1481,15 +1425,11 @@
       <c r="D20" s="3" t="n">
         <v>-2.128946</v>
       </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E20" s="3" t="n">
+        <v>-1.427049</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>-2.037757</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.692613</v>
@@ -1536,15 +1476,11 @@
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1591,15 +1527,11 @@
       <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1646,15 +1578,11 @@
       <c r="D23" s="3" t="n">
         <v>-2.128946</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>-1.427049</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>-2.037757</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>-0.692613</v>
@@ -1701,15 +1629,11 @@
       <c r="D24" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>-0.01</v>
@@ -1756,15 +1680,11 @@
       <c r="D25" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>-0.01</v>
@@ -1811,15 +1731,11 @@
       <c r="D26" s="3" t="n">
         <v>53.22365</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>71.35245</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>67.92523300000001</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1878,15 +1794,11 @@
       <c r="D27" s="3" t="n">
         <v>-2.102134</v>
       </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="3" t="n">
+        <v>-1.412732</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>-2.029346</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-0.684793</v>
@@ -1933,15 +1845,11 @@
       <c r="D28" s="3" t="n">
         <v>0.007484</v>
       </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="3" t="n">
+        <v>0.007166</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>0.007166</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.003169</v>
@@ -1988,15 +1896,11 @@
       <c r="D29" s="3" t="n">
         <v>-2.09465</v>
       </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="3" t="n">
+        <v>-1.405566</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>-2.02218</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-0.681624</v>
@@ -2120,15 +2024,11 @@
       <c r="D31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -4073,22 +3973,22 @@
         <v>0</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.050018</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>0.039416</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>0.03603</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.035662</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.036201</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.037303</v>
       </c>
     </row>
     <row r="71">
@@ -4122,22 +4022,22 @@
         <v>0</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.050018</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.039416</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.03603</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.035662</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.036201</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.037303</v>
       </c>
     </row>
     <row r="72">
@@ -4318,22 +4218,22 @@
         <v>0</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.813507</v>
+        <v>0.763489</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.853203</v>
+        <v>0.813787</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.7234080000000001</v>
+        <v>0.687378</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.183411</v>
+        <v>0.147749</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.382355</v>
+        <v>0.346154</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.856963</v>
+        <v>0.8196600000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4578,35 +4478,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J80" s="3" t="n">
+        <v>0.002237169485469804</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.001370961071675846</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.0009119985675319752</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.0008467082264867343</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>0.001081811497700945</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.0009522095854573706</v>
       </c>
     </row>
     <row r="81">
@@ -5474,15 +5362,11 @@
       <c r="D99" s="3" t="n">
         <v>-2.128946</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-1.427049</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-2.037757</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>-0.692613</v>
@@ -5527,15 +5411,11 @@
       <c r="D100" s="3" t="n">
         <v>0.007484</v>
       </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E100" s="3" t="n">
+        <v>0.007166</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.007166</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0.003169</v>
@@ -5580,15 +5460,11 @@
       <c r="D101" s="3" t="n">
         <v>0.071719</v>
       </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E101" s="3" t="n">
+        <v>-0.029748</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.002252</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.032732</v>
@@ -5633,15 +5509,11 @@
       <c r="D102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
@@ -5686,15 +5558,11 @@
       <c r="D103" s="3" t="n">
         <v>-0.009292</v>
       </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E103" s="3" t="n">
+        <v>-0.00411</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>0.000645</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>0.008404999999999999</v>
@@ -5739,15 +5607,11 @@
       <c r="D104" s="3" t="n">
         <v>-0.040954</v>
       </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="3" t="n">
+        <v>-0.104741</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>0.019195</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0.015817</v>
@@ -5792,15 +5656,11 @@
       <c r="D105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>0</v>
@@ -5845,15 +5705,11 @@
       <c r="D106" s="3" t="n">
         <v>0.021473</v>
       </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E106" s="3" t="n">
+        <v>-0.138599</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>0.022092</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.00851</v>
@@ -5898,15 +5754,11 @@
       <c r="D107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>0</v>
@@ -5951,15 +5803,11 @@
       <c r="D108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
         <v>0</v>
@@ -6004,15 +5852,11 @@
       <c r="D109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>0</v>
@@ -6057,15 +5901,11 @@
       <c r="D110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -6110,15 +5950,11 @@
       <c r="D111" s="3" t="n">
         <v>-0.035333</v>
       </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E111" s="3" t="n">
+        <v>-0.005897</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>-0.00437</v>
@@ -6163,15 +5999,11 @@
       <c r="D112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -6216,15 +6048,11 @@
       <c r="D113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G113" s="3" t="n">
         <v>0</v>
@@ -6269,15 +6097,11 @@
       <c r="D114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
         <v>0</v>
@@ -6322,15 +6146,11 @@
       <c r="D115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -6375,15 +6195,11 @@
       <c r="D116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G116" s="3" t="n">
         <v>0</v>
@@ -6428,15 +6244,11 @@
       <c r="D117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
@@ -6481,15 +6293,11 @@
       <c r="D118" s="3" t="n">
         <v>-2.599195</v>
       </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>0</v>
@@ -6534,15 +6342,11 @@
       <c r="D119" s="3" t="n">
         <v>3.543426</v>
       </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E119" s="3" t="n">
+        <v>1.394418</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>0.912155</v>
       </c>
       <c r="G119" s="3" t="n">
         <v>-0.673971</v>
@@ -6587,15 +6391,11 @@
       <c r="D120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
@@ -6640,15 +6440,11 @@
       <c r="D121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
         <v>0</v>
@@ -6693,15 +6489,11 @@
       <c r="D122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
@@ -6746,15 +6538,11 @@
       <c r="D123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>0</v>
@@ -6799,15 +6587,11 @@
       <c r="D124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -6852,15 +6636,11 @@
       <c r="D125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -6905,15 +6685,11 @@
       <c r="D126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>0</v>
@@ -7035,15 +6811,11 @@
       <c r="D128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>0</v>
@@ -7088,15 +6860,11 @@
       <c r="D129" s="3" t="n">
         <v>1.873151</v>
       </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E129" s="3" t="n">
+        <v>0.859558</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>0.908138</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>5.916843</v>
@@ -7206,15 +6974,11 @@
       <c r="D131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G131" s="3" t="n">
         <v>0</v>
@@ -7259,15 +7023,11 @@
       <c r="D132" s="3" t="n">
         <v>-1.750757</v>
       </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E132" s="3" t="n">
+        <v>-0.748686</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>-0.482263</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>4.6532</v>
@@ -7377,15 +7137,11 @@
       <c r="D134" s="3" t="n">
         <v>-0.035333</v>
       </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E134" s="3" t="n">
+        <v>-0.005897</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>-0.00437</v>
@@ -7430,15 +7186,11 @@
       <c r="D135" s="3" t="n">
         <v>-1.024713</v>
       </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E135" s="3" t="n">
+        <v>-0.807525</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>-0.607132</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.594042</v>
@@ -7479,7 +7231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R348"/>
+  <dimension ref="A1:R355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8388,7 +8140,11 @@
           <t>Current portion of lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -9538,7 +9294,11 @@
           <t>Current portion of lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -11122,7 +10882,11 @@
           <t>Current portion of lease obligations (note 2.15 and 8)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -21126,15 +20890,11 @@
       <c r="G164" s="5" t="n">
         <v>0.007484</v>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>0.007166</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.007166</v>
       </c>
       <c r="J164" s="5" t="n">
         <v>0.003169</v>
@@ -21446,15 +21206,11 @@
       <c r="G168" s="5" t="n">
         <v>-0.026812</v>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>-0.014317</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>-0.008411</v>
       </c>
       <c r="J168" s="5" t="n">
         <v>-0.007820000000000001</v>
@@ -21516,15 +21272,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H169" s="5" t="n">
+        <v>0.014066</v>
+      </c>
+      <c r="I169" s="5" t="n">
+        <v>0.007884</v>
       </c>
       <c r="J169" s="5" t="n">
         <v>0.007165</v>
@@ -21580,15 +21332,11 @@
       <c r="G170" s="5" t="n">
         <v>-1.010853</v>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H170" s="5" t="n">
+        <v>-0.663029</v>
+      </c>
+      <c r="I170" s="5" t="n">
+        <v>-0.629224</v>
       </c>
       <c r="J170" s="5" t="n">
         <v>-0.581162</v>
@@ -21648,15 +21396,11 @@
       <c r="G171" s="5" t="n">
         <v>0.071719</v>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H171" s="5" t="n">
+        <v>-0.029748</v>
+      </c>
+      <c r="I171" s="5" t="n">
+        <v>0.002252</v>
       </c>
       <c r="J171" s="5" t="n">
         <v>-0.032732</v>
@@ -21716,15 +21460,11 @@
       <c r="G172" s="5" t="n">
         <v>-0.009292</v>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H172" s="5" t="n">
+        <v>-0.00411</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>0.000645</v>
       </c>
       <c r="J172" s="5" t="n">
         <v>0.008404999999999999</v>
@@ -21784,15 +21524,11 @@
       <c r="G173" s="5" t="n">
         <v>-0.040954</v>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H173" s="5" t="n">
+        <v>-0.104741</v>
+      </c>
+      <c r="I173" s="5" t="n">
+        <v>0.019195</v>
       </c>
       <c r="J173" s="5" t="n">
         <v>0.015817</v>
@@ -22598,10 +22334,8 @@
       <c r="G183" s="5" t="n">
         <v>-0.035333</v>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H183" s="5" t="n">
+        <v>-0.005897</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -24924,15 +24658,11 @@
       <c r="G211" s="5" t="n">
         <v>-0.98938</v>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>-0.801628</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>-0.607132</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -25258,15 +24988,11 @@
       <c r="G215" s="5" t="n">
         <v>1.873151</v>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>0.859558</v>
+      </c>
+      <c r="I215" s="5" t="n">
+        <v>0.908138</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -25422,15 +25148,11 @@
       <c r="G217" s="5" t="n">
         <v>-2.634528</v>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>-0.806616</v>
+      </c>
+      <c r="I217" s="5" t="n">
+        <v>-0.783269</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -25502,15 +25224,11 @@
       <c r="G218" s="5" t="n">
         <v>-1.750757</v>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>-0.748686</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>-0.482263</v>
       </c>
       <c r="J218" s="5" t="n">
         <v>4.6532</v>
@@ -26894,15 +26612,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H235" s="5" t="n">
+        <v>2.143104</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>1.394418</v>
       </c>
       <c r="J235" s="5" t="n">
         <v>0.912155</v>
@@ -26974,15 +26688,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H236" s="5" t="n">
+        <v>1.394418</v>
+      </c>
+      <c r="I236" s="5" t="n">
+        <v>0.912155</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -27052,15 +26762,11 @@
       <c r="G237" s="5" t="n">
         <v>0.134823</v>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H237" s="5" t="n">
+        <v>0.097349</v>
+      </c>
+      <c r="I237" s="5" t="n">
+        <v>0.08643099999999999</v>
       </c>
       <c r="J237" s="5" t="n">
         <v>0.125202</v>
@@ -27902,15 +27608,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H247" s="5" t="n">
+        <v>-0.800719</v>
+      </c>
+      <c r="I247" s="5" t="n">
+        <v>-0.783269</v>
       </c>
       <c r="J247" s="5" t="n">
         <v>-0.769259</v>
@@ -28051,28 +27753,30 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Loss before deferred income and mining taxes for the year</t>
+          <t>Loss before deferred income and mining taxes</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" s="5" t="n">
-        <v>-0.933592</v>
-      </c>
-      <c r="F249" s="5" t="n">
-        <v>-1.586581</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>-2.109595</v>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" s="5" t="n">
+        <v>-1.664137</v>
+      </c>
+      <c r="I249" s="5" t="n">
+        <v>-2.669526</v>
       </c>
       <c r="J249" t="inlineStr">
         <is>
@@ -28133,30 +27837,26 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Write-off of exploration assets and deferred exploration cost</t>
+          <t>Write-off of deferred exploration costs</t>
         </is>
       </c>
       <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E250" s="5" t="n">
+        <v>0.047275</v>
       </c>
       <c r="F250" s="5" t="n">
-        <v>0.389319</v>
-      </c>
-      <c r="G250" s="5" t="n">
-        <v>0.9580689999999999</v>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.260304</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" s="5" t="n">
+        <v>0.816844</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>1.871482</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -28217,7 +27917,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Interest income received</t>
+          <t>Impairment of securities available-for-sale</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -28226,21 +27926,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F251" s="5" t="n">
-        <v>0.033658</v>
-      </c>
-      <c r="G251" s="5" t="n">
-        <v>0.025178</v>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>0.07575</v>
       </c>
       <c r="J251" t="inlineStr">
         <is>
@@ -28301,28 +28001,30 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Issuance of shares and warrants</t>
+          <t>Share issue</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" s="5" t="n">
-        <v>4.91754</v>
-      </c>
-      <c r="F252" s="5" t="n">
-        <v>3.08084</v>
-      </c>
-      <c r="G252" s="5" t="n">
-        <v>2.0004</v>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" s="5" t="n">
+        <v>0.87576</v>
+      </c>
+      <c r="I252" s="5" t="n">
+        <v>0.9495</v>
       </c>
       <c r="J252" t="inlineStr">
         <is>
@@ -28383,30 +28085,30 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Exercise of stock options</t>
+          <t>Share issue expenses</t>
         </is>
       </c>
       <c r="D253" t="inlineStr"/>
-      <c r="E253" s="5" t="n">
-        <v>0.00975</v>
-      </c>
-      <c r="F253" s="5" t="n">
-        <v>0.04805</v>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H253" s="5" t="n">
+        <v>-0.016202</v>
+      </c>
+      <c r="I253" s="5" t="n">
+        <v>-0.041362</v>
       </c>
       <c r="J253" t="inlineStr">
         <is>
@@ -28462,33 +28164,31 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Share and warrant issue expenses</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" s="5" t="n">
-        <v>-0.440948</v>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F254" s="5" t="n">
-        <v>-0.308816</v>
+        <v>3.263143</v>
       </c>
       <c r="G254" s="5" t="n">
-        <v>-0.127249</v>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.670297</v>
+      </c>
+      <c r="H254" s="5" t="n">
+        <v>0.857196</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>0.83693</v>
       </c>
       <c r="J254" t="inlineStr">
         <is>
@@ -28549,32 +28249,24 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Sale of mining proprety and deferred exploration costs</t>
+          <t>Cash reserved for exploration</t>
         </is>
       </c>
       <c r="D255" t="inlineStr"/>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E255" s="5" t="n">
+        <v>-1.065574</v>
       </c>
       <c r="F255" s="5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.03104</v>
+      </c>
+      <c r="G255" s="5" t="n">
+        <v>0.873129</v>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>0.537222</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>0.075225</v>
       </c>
       <c r="J255" t="inlineStr">
         <is>
@@ -28635,12 +28327,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Acquisition of Exploration and evaluation assets</t>
+          <t>INVESTING ACTIVITIES total</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -28649,20 +28341,16 @@
         </is>
       </c>
       <c r="F256" s="5" t="n">
-        <v>-2.072486</v>
+        <v>5.294183</v>
       </c>
       <c r="G256" s="5" t="n">
-        <v>-2.599195</v>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.543426</v>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>1.394418</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>0.912155</v>
       </c>
       <c r="J256" t="inlineStr">
         <is>
@@ -28718,27 +28406,23 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Loss before deferred income and mining taxes for the year</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" s="5" t="n">
-        <v>1.484131</v>
+        <v>-0.933592</v>
       </c>
       <c r="F257" s="5" t="n">
-        <v>4.692175</v>
+        <v>-1.586581</v>
       </c>
       <c r="G257" s="5" t="n">
-        <v>5.294183</v>
+        <v>-2.109595</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -28804,27 +28488,25 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E258" s="5" t="n">
-        <v>3.432175</v>
+          <t>Write-off of exploration assets and deferred exploration cost</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F258" s="5" t="n">
-        <v>5.294183</v>
+        <v>0.389319</v>
       </c>
       <c r="G258" s="5" t="n">
-        <v>3.543426</v>
+        <v>0.9580689999999999</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -28890,12 +28572,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Interest income received</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -28905,10 +28587,10 @@
         </is>
       </c>
       <c r="F259" s="5" t="n">
-        <v>3.263143</v>
+        <v>0.033658</v>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2.670297</v>
+        <v>0.025178</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -28974,23 +28656,23 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cash reserved for exploration</t>
+          <t>Issuance of shares and warrants</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
       <c r="E260" s="5" t="n">
-        <v>-1.065574</v>
+        <v>4.91754</v>
       </c>
       <c r="F260" s="5" t="n">
-        <v>2.03104</v>
+        <v>3.08084</v>
       </c>
       <c r="G260" s="5" t="n">
-        <v>0.873129</v>
+        <v>2.0004</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -29056,29 +28738,25 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES total</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exercise of stock options</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="5" t="n">
+        <v>0.00975</v>
       </c>
       <c r="F261" s="5" t="n">
-        <v>5.294183</v>
-      </c>
-      <c r="G261" s="5" t="n">
-        <v>3.543426</v>
+        <v>0.04805</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -29144,29 +28822,23 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Share and warrant issue expenses</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
       <c r="E262" s="5" t="n">
-        <v>0.113173</v>
+        <v>-0.440948</v>
       </c>
       <c r="F262" s="5" t="n">
-        <v>0.236177</v>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.308816</v>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>-0.127249</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -29232,20 +28904,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Write-off of mining properties</t>
+          <t>Sale of mining proprety and deferred exploration costs</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
-      <c r="E263" s="5" t="n">
-        <v>0.058714</v>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F263" s="5" t="n">
-        <v>0.129015</v>
+        <v>0.15</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -29316,25 +28990,29 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Write-off of deferred exploration costs</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" s="5" t="n">
-        <v>0.047275</v>
+          <t>Acquisition of Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F264" s="5" t="n">
-        <v>0.260304</v>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.072486</v>
+      </c>
+      <c r="G264" s="5" t="n">
+        <v>-2.599195</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -29400,27 +29078,27 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Shares to be issued from exercice of warrants</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr"/>
+          <t>Cash and cash equivalents, beginning of year</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="n">
-        <v>0.312662</v>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.484131</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>4.692175</v>
+      </c>
+      <c r="G265" s="5" t="n">
+        <v>5.294183</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -29491,20 +29169,22 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Acquisition of mining properties</t>
-        </is>
-      </c>
-      <c r="D266" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E266" s="5" t="n">
-        <v>-0.029172</v>
+        <v>3.432175</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>-0.006464</v>
-      </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.294183</v>
+      </c>
+      <c r="G266" s="5" t="n">
+        <v>3.543426</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -29570,20 +29250,24 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Deferred exploration costs</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr"/>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
-        <v>-1.309974</v>
+        <v>0.113173</v>
       </c>
       <c r="F267" s="5" t="n">
-        <v>-2.066022</v>
+        <v>0.236177</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -29649,29 +29333,25 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Salaries (note 12)</t>
+          <t>Write-off of mining properties</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E268" s="5" t="n">
+        <v>0.058714</v>
+      </c>
+      <c r="F268" s="5" t="n">
+        <v>0.129015</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -29723,40 +29403,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q268" s="5" t="n">
-        <v>0.5825939999999999</v>
-      </c>
-      <c r="R268" s="5" t="n">
-        <v>0.6584179999999999</v>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Consultants</t>
+          <t>Shares to be issued from exercice of warrants</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>0.127783</v>
-      </c>
-      <c r="G269" s="5" t="n">
-        <v>0.144174</v>
+      <c r="E269" s="5" t="n">
+        <v>0.312662</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -29768,60 +29454,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J269" s="5" t="n">
-        <v>0.011645</v>
-      </c>
-      <c r="K269" s="5" t="n">
-        <v>0.013913</v>
-      </c>
-      <c r="L269" s="5" t="n">
-        <v>0.027409</v>
-      </c>
-      <c r="M269" s="5" t="n">
-        <v>0.006221</v>
-      </c>
-      <c r="N269" s="5" t="n">
-        <v>0.006133</v>
-      </c>
-      <c r="O269" s="5" t="n">
-        <v>0.008156</v>
-      </c>
-      <c r="P269" s="5" t="n">
-        <v>0.001387</v>
-      </c>
-      <c r="Q269" s="5" t="n">
-        <v>0.001723</v>
-      </c>
-      <c r="R269" s="5" t="n">
-        <v>0.009514999999999999</v>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Share-based payments (note 11)</t>
+          <t>Acquisition of mining properties</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E270" s="5" t="n">
+        <v>-0.029172</v>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>-0.006464</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
@@ -29873,44 +29573,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q270" s="5" t="n">
-        <v>0.287999</v>
-      </c>
-      <c r="R270" s="5" t="n">
-        <v>0.483519</v>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred exploration costs</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" s="5" t="n">
+        <v>-1.309974</v>
       </c>
       <c r="F271" s="5" t="n">
-        <v>0.10218</v>
-      </c>
-      <c r="G271" s="5" t="n">
-        <v>0.121247</v>
+        <v>-2.066022</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -29922,32 +29622,50 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J271" s="5" t="n">
-        <v>0.06894400000000001</v>
-      </c>
-      <c r="K271" s="5" t="n">
-        <v>0.07120799999999999</v>
-      </c>
-      <c r="L271" s="5" t="n">
-        <v>0.069232</v>
-      </c>
-      <c r="M271" s="5" t="n">
-        <v>0.036677</v>
-      </c>
-      <c r="N271" s="5" t="n">
-        <v>0.095093</v>
-      </c>
-      <c r="O271" s="5" t="n">
-        <v>0.092879</v>
-      </c>
-      <c r="P271" s="5" t="n">
-        <v>0.100174</v>
-      </c>
-      <c r="Q271" s="5" t="n">
-        <v>0.131422</v>
-      </c>
-      <c r="R271" s="5" t="n">
-        <v>0.123325</v>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -29963,7 +29681,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Business development expenditures (analysts and brokers)</t>
+          <t>Salaries (note 12)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -30002,26 +29720,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L272" s="5" t="n">
-        <v>0.097459</v>
-      </c>
-      <c r="M272" s="5" t="n">
-        <v>0.129182</v>
-      </c>
-      <c r="N272" s="5" t="n">
-        <v>0.166481</v>
-      </c>
-      <c r="O272" s="5" t="n">
-        <v>0.25787</v>
-      </c>
-      <c r="P272" s="5" t="n">
-        <v>0.378463</v>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q272" s="5" t="n">
-        <v>0.143897</v>
+        <v>0.5825939999999999</v>
       </c>
       <c r="R272" s="5" t="n">
-        <v>0.187362</v>
+        <v>0.6584179999999999</v>
       </c>
     </row>
     <row r="273">
@@ -30037,7 +29765,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Road shows and gold shows</t>
+          <t>Consultants</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -30046,56 +29774,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F273" s="5" t="n">
+        <v>0.127783</v>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>0.144174</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>0.099592</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>0.046976</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>0.011645</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>0.013913</v>
       </c>
       <c r="L273" s="5" t="n">
-        <v>0.150455</v>
+        <v>0.027409</v>
       </c>
       <c r="M273" s="5" t="n">
-        <v>0.110706</v>
+        <v>0.006221</v>
       </c>
       <c r="N273" s="5" t="n">
-        <v>0.014893</v>
+        <v>0.006133</v>
       </c>
       <c r="O273" s="5" t="n">
-        <v>0.078308</v>
+        <v>0.008156</v>
       </c>
       <c r="P273" s="5" t="n">
-        <v>0.100292</v>
+        <v>0.001387</v>
       </c>
       <c r="Q273" s="5" t="n">
-        <v>0.029156</v>
+        <v>0.001723</v>
       </c>
       <c r="R273" s="5" t="n">
-        <v>0.229249</v>
+        <v>0.009514999999999999</v>
       </c>
     </row>
     <row r="274">
@@ -30111,14 +29827,10 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payments (note 11)</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -30154,26 +29866,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L274" s="5" t="n">
-        <v>0.270559</v>
-      </c>
-      <c r="M274" s="5" t="n">
-        <v>0.149201</v>
-      </c>
-      <c r="N274" s="5" t="n">
-        <v>0.080136</v>
-      </c>
-      <c r="O274" s="5" t="n">
-        <v>0.141322</v>
-      </c>
-      <c r="P274" s="5" t="n">
-        <v>0.16301</v>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q274" s="5" t="n">
-        <v>0.064843</v>
+        <v>0.287999</v>
       </c>
       <c r="R274" s="5" t="n">
-        <v>0.235223</v>
+        <v>0.483519</v>
       </c>
     </row>
     <row r="275">
@@ -30189,57 +29911,57 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Insurance, taxes and permits</t>
-        </is>
-      </c>
-      <c r="D275" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F275" s="5" t="n">
-        <v>0.017965</v>
+        <v>0.10218</v>
       </c>
       <c r="G275" s="5" t="n">
-        <v>0.019366</v>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.121247</v>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>0.076336</v>
+      </c>
+      <c r="I275" s="5" t="n">
+        <v>0.094651</v>
       </c>
       <c r="J275" s="5" t="n">
-        <v>0.014059</v>
+        <v>0.06894400000000001</v>
       </c>
       <c r="K275" s="5" t="n">
-        <v>0.016263</v>
+        <v>0.07120799999999999</v>
       </c>
       <c r="L275" s="5" t="n">
-        <v>0.016</v>
+        <v>0.069232</v>
       </c>
       <c r="M275" s="5" t="n">
-        <v>0.016661</v>
+        <v>0.036677</v>
       </c>
       <c r="N275" s="5" t="n">
-        <v>0.021545</v>
+        <v>0.095093</v>
       </c>
       <c r="O275" s="5" t="n">
-        <v>0.025951</v>
+        <v>0.092879</v>
       </c>
       <c r="P275" s="5" t="n">
-        <v>0.027272</v>
+        <v>0.100174</v>
       </c>
       <c r="Q275" s="5" t="n">
-        <v>0.02765</v>
+        <v>0.131422</v>
       </c>
       <c r="R275" s="5" t="n">
-        <v>0.028979</v>
+        <v>0.123325</v>
       </c>
     </row>
     <row r="276">
@@ -30255,24 +29977,24 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Depreciation of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Business development expenditures (analysts and brokers)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F276" s="5" t="n">
-        <v>0.004643</v>
-      </c>
-      <c r="G276" s="5" t="n">
-        <v>0.007484</v>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -30284,38 +30006,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J276" s="5" t="n">
-        <v>0.003169</v>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L276" s="5" t="n">
+        <v>0.097459</v>
+      </c>
+      <c r="M276" s="5" t="n">
+        <v>0.129182</v>
       </c>
       <c r="N276" s="5" t="n">
-        <v>0.00066</v>
+        <v>0.166481</v>
       </c>
       <c r="O276" s="5" t="n">
-        <v>0.00278</v>
+        <v>0.25787</v>
       </c>
       <c r="P276" s="5" t="n">
-        <v>0.003071</v>
+        <v>0.378463</v>
       </c>
       <c r="Q276" s="5" t="n">
-        <v>0.003243</v>
+        <v>0.143897</v>
       </c>
       <c r="R276" s="5" t="n">
-        <v>0.00474</v>
+        <v>0.187362</v>
       </c>
     </row>
     <row r="277">
@@ -30331,14 +30051,10 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Depreciation of right-of-use assets</t>
-        </is>
-      </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>DepreciationAmortizationDepletion</t>
-        </is>
-      </c>
+          <t>Road shows and gold shows</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -30374,28 +30090,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L277" s="5" t="n">
+        <v>0.150455</v>
       </c>
       <c r="M277" s="5" t="n">
-        <v>0.007867000000000001</v>
+        <v>0.110706</v>
       </c>
       <c r="N277" s="5" t="n">
-        <v>0.019668</v>
+        <v>0.014893</v>
       </c>
       <c r="O277" s="5" t="n">
-        <v>0.020784</v>
+        <v>0.078308</v>
       </c>
       <c r="P277" s="5" t="n">
-        <v>0.019668</v>
+        <v>0.100292</v>
       </c>
       <c r="Q277" s="5" t="n">
-        <v>0.021097</v>
+        <v>0.029156</v>
       </c>
       <c r="R277" s="5" t="n">
-        <v>0.021573</v>
+        <v>0.229249</v>
       </c>
     </row>
     <row r="278">
@@ -30411,10 +30125,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Loss on disposal of property, plant and equipment</t>
-        </is>
-      </c>
-      <c r="D278" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -30450,36 +30168,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P278" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L278" s="5" t="n">
+        <v>0.270559</v>
+      </c>
+      <c r="M278" s="5" t="n">
+        <v>0.149201</v>
+      </c>
+      <c r="N278" s="5" t="n">
+        <v>0.080136</v>
+      </c>
+      <c r="O278" s="5" t="n">
+        <v>0.141322</v>
+      </c>
+      <c r="P278" s="5" t="n">
+        <v>0.16301</v>
       </c>
       <c r="Q278" s="5" t="n">
-        <v>0.001136</v>
+        <v>0.064843</v>
       </c>
       <c r="R278" s="5" t="n">
-        <v>5.7e-05</v>
+        <v>0.235223</v>
       </c>
     </row>
     <row r="279">
@@ -30495,7 +30203,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Office supplies</t>
+          <t>Insurance, taxes and permits</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -30504,52 +30212,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I279" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F279" s="5" t="n">
+        <v>0.017965</v>
+      </c>
+      <c r="G279" s="5" t="n">
+        <v>0.019366</v>
+      </c>
+      <c r="H279" s="5" t="n">
+        <v>0.019041</v>
+      </c>
+      <c r="I279" s="5" t="n">
+        <v>0.016645</v>
       </c>
       <c r="J279" s="5" t="n">
-        <v>0.02068</v>
+        <v>0.014059</v>
       </c>
       <c r="K279" s="5" t="n">
-        <v>0.026225</v>
+        <v>0.016263</v>
       </c>
       <c r="L279" s="5" t="n">
-        <v>0.02214</v>
+        <v>0.016</v>
       </c>
       <c r="M279" s="5" t="n">
-        <v>0.024329</v>
+        <v>0.016661</v>
       </c>
       <c r="N279" s="5" t="n">
-        <v>0.02772</v>
+        <v>0.021545</v>
       </c>
       <c r="O279" s="5" t="n">
-        <v>0.046157</v>
+        <v>0.025951</v>
       </c>
       <c r="P279" s="5" t="n">
-        <v>0.06539200000000001</v>
+        <v>0.027272</v>
       </c>
       <c r="Q279" s="5" t="n">
-        <v>0.039045</v>
+        <v>0.02765</v>
       </c>
       <c r="R279" s="5" t="n">
-        <v>0.073573</v>
+        <v>0.028979</v>
       </c>
     </row>
     <row r="280">
@@ -30565,57 +30265,63 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Telecommunications</t>
-        </is>
-      </c>
-      <c r="D280" t="inlineStr"/>
+          <t>Depreciation of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F280" s="5" t="n">
-        <v>0.01192</v>
+        <v>0.004643</v>
       </c>
       <c r="G280" s="5" t="n">
-        <v>0.007854</v>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007484</v>
+      </c>
+      <c r="H280" s="5" t="n">
+        <v>0.007166</v>
+      </c>
+      <c r="I280" s="5" t="n">
+        <v>0.007166</v>
       </c>
       <c r="J280" s="5" t="n">
-        <v>0.005852</v>
-      </c>
-      <c r="K280" s="5" t="n">
-        <v>0.006184</v>
-      </c>
-      <c r="L280" s="5" t="n">
-        <v>0.005299</v>
-      </c>
-      <c r="M280" s="5" t="n">
-        <v>0.008853</v>
+        <v>0.003169</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N280" s="5" t="n">
-        <v>0.008682</v>
+        <v>0.00066</v>
       </c>
       <c r="O280" s="5" t="n">
-        <v>0.008229999999999999</v>
+        <v>0.00278</v>
       </c>
       <c r="P280" s="5" t="n">
-        <v>0.005487</v>
+        <v>0.003071</v>
       </c>
       <c r="Q280" s="5" t="n">
-        <v>0.006068</v>
+        <v>0.003243</v>
       </c>
       <c r="R280" s="5" t="n">
-        <v>0.007286</v>
+        <v>0.00474</v>
       </c>
     </row>
     <row r="281">
@@ -30631,20 +30337,28 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Training and travel</t>
-        </is>
-      </c>
-      <c r="D281" t="inlineStr"/>
+          <t>Depreciation of right-of-use assets</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F281" s="5" t="n">
-        <v>0.051534</v>
-      </c>
-      <c r="G281" s="5" t="n">
-        <v>0.040846</v>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -30656,32 +30370,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J281" s="5" t="n">
-        <v>0.010668</v>
-      </c>
-      <c r="K281" s="5" t="n">
-        <v>0.020547</v>
-      </c>
-      <c r="L281" s="5" t="n">
-        <v>0.02616</v>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M281" s="5" t="n">
-        <v>0.027654</v>
+        <v>0.007867000000000001</v>
       </c>
       <c r="N281" s="5" t="n">
-        <v>0.017196</v>
+        <v>0.019668</v>
       </c>
       <c r="O281" s="5" t="n">
-        <v>0.021442</v>
+        <v>0.020784</v>
       </c>
       <c r="P281" s="5" t="n">
-        <v>0.011787</v>
+        <v>0.019668</v>
       </c>
       <c r="Q281" s="5" t="n">
-        <v>0.018504</v>
+        <v>0.021097</v>
       </c>
       <c r="R281" s="5" t="n">
-        <v>0.013898</v>
+        <v>0.021573</v>
       </c>
     </row>
     <row r="282">
@@ -30697,7 +30417,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Advertising and sponsoring</t>
+          <t>Loss on disposal of property, plant and equipment</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -30726,32 +30446,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J282" s="5" t="n">
-        <v>0.006711</v>
-      </c>
-      <c r="K282" s="5" t="n">
-        <v>0.030225</v>
-      </c>
-      <c r="L282" s="5" t="n">
-        <v>0.020964</v>
-      </c>
-      <c r="M282" s="5" t="n">
-        <v>0.016527</v>
-      </c>
-      <c r="N282" s="5" t="n">
-        <v>0.01297</v>
-      </c>
-      <c r="O282" s="5" t="n">
-        <v>0.018143</v>
-      </c>
-      <c r="P282" s="5" t="n">
-        <v>0.010868</v>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q282" s="5" t="n">
-        <v>0.007027</v>
+        <v>0.001136</v>
       </c>
       <c r="R282" s="5" t="n">
-        <v>0.038886</v>
+        <v>5.7e-05</v>
       </c>
     </row>
     <row r="283">
@@ -30767,7 +30501,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Information to shareholders</t>
+          <t>Office supplies</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -30786,54 +30520,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H283" s="5" t="n">
+        <v>0.023013</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>0.024073</v>
+      </c>
+      <c r="J283" s="5" t="n">
+        <v>0.02068</v>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>0.026225</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="M283" s="5" t="n">
+        <v>0.024329</v>
+      </c>
+      <c r="N283" s="5" t="n">
+        <v>0.02772</v>
+      </c>
+      <c r="O283" s="5" t="n">
+        <v>0.046157</v>
       </c>
       <c r="P283" s="5" t="n">
-        <v>0.040485</v>
+        <v>0.06539200000000001</v>
       </c>
       <c r="Q283" s="5" t="n">
-        <v>0.042719</v>
+        <v>0.039045</v>
       </c>
       <c r="R283" s="5" t="n">
-        <v>0.03883</v>
+        <v>0.073573</v>
       </c>
     </row>
     <row r="284">
@@ -30849,7 +30567,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Part XII.6 tax related to flow-through shares</t>
+          <t>Telecommunications</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -30859,55 +30577,43 @@
         </is>
       </c>
       <c r="F284" s="5" t="n">
-        <v>0.002471</v>
+        <v>0.01192</v>
       </c>
       <c r="G284" s="5" t="n">
-        <v>0.004081</v>
-      </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007854</v>
+      </c>
+      <c r="H284" s="5" t="n">
+        <v>0.007635</v>
+      </c>
+      <c r="I284" s="5" t="n">
+        <v>0.007913999999999999</v>
+      </c>
+      <c r="J284" s="5" t="n">
+        <v>0.005852</v>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>0.006184</v>
       </c>
       <c r="L284" s="5" t="n">
-        <v>0.006531</v>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005299</v>
+      </c>
+      <c r="M284" s="5" t="n">
+        <v>0.008853</v>
+      </c>
+      <c r="N284" s="5" t="n">
+        <v>0.008682</v>
       </c>
       <c r="O284" s="5" t="n">
-        <v>0.020209</v>
+        <v>0.008229999999999999</v>
       </c>
       <c r="P284" s="5" t="n">
-        <v>0.006215</v>
+        <v>0.005487</v>
       </c>
       <c r="Q284" s="5" t="n">
-        <v>0.044863</v>
+        <v>0.006068</v>
       </c>
       <c r="R284" s="5" t="n">
-        <v>0.012944</v>
+        <v>0.007286</v>
       </c>
     </row>
     <row r="285">
@@ -30923,61 +30629,53 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Administrative expenses total</t>
-        </is>
-      </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Training and travel</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F285" s="5" t="n">
-        <v>1.189871</v>
+        <v>0.051534</v>
       </c>
       <c r="G285" s="5" t="n">
-        <v>1.102966</v>
-      </c>
-      <c r="H285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I285" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.040846</v>
+      </c>
+      <c r="H285" s="5" t="n">
+        <v>0.029561</v>
+      </c>
+      <c r="I285" s="5" t="n">
+        <v>0.013569</v>
       </c>
       <c r="J285" s="5" t="n">
-        <v>0.861418</v>
+        <v>0.010668</v>
       </c>
       <c r="K285" s="5" t="n">
-        <v>1.421323</v>
+        <v>0.020547</v>
       </c>
       <c r="L285" s="5" t="n">
-        <v>1.566859</v>
+        <v>0.02616</v>
       </c>
       <c r="M285" s="5" t="n">
-        <v>1.194335</v>
+        <v>0.027654</v>
       </c>
       <c r="N285" s="5" t="n">
-        <v>1.401986</v>
+        <v>0.017196</v>
       </c>
       <c r="O285" s="5" t="n">
-        <v>1.505011</v>
+        <v>0.021442</v>
       </c>
       <c r="P285" s="5" t="n">
-        <v>1.713301</v>
+        <v>0.011787</v>
       </c>
       <c r="Q285" s="5" t="n">
-        <v>1.452986</v>
+        <v>0.018504</v>
       </c>
       <c r="R285" s="5" t="n">
-        <v>2.167377</v>
+        <v>0.013898</v>
       </c>
     </row>
     <row r="286">
@@ -30988,12 +30686,12 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Sale of property option (note 9 (a) (b) (c) (d))</t>
+          <t>Advertising and sponsoring</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -31012,56 +30710,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P286" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H286" s="5" t="n">
+        <v>0.013496</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>0.008284</v>
+      </c>
+      <c r="J286" s="5" t="n">
+        <v>0.006711</v>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>0.030225</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>0.020964</v>
+      </c>
+      <c r="M286" s="5" t="n">
+        <v>0.016527</v>
+      </c>
+      <c r="N286" s="5" t="n">
+        <v>0.01297</v>
+      </c>
+      <c r="O286" s="5" t="n">
+        <v>0.018143</v>
+      </c>
+      <c r="P286" s="5" t="n">
+        <v>0.010868</v>
       </c>
       <c r="Q286" s="5" t="n">
-        <v>-0.028</v>
+        <v>0.007027</v>
       </c>
       <c r="R286" s="5" t="n">
-        <v>-0.25775</v>
+        <v>0.038886</v>
       </c>
     </row>
     <row r="287">
@@ -31072,12 +30752,12 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Write-down of mining assets and deferred exploration costs (note 9)</t>
+          <t>Information to shareholders</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -31136,16 +30816,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P287" s="5" t="n">
+        <v>0.040485</v>
       </c>
       <c r="Q287" s="5" t="n">
-        <v>9.921411000000001</v>
+        <v>0.042719</v>
       </c>
       <c r="R287" s="5" t="n">
-        <v>3.388054</v>
+        <v>0.03883</v>
       </c>
     </row>
     <row r="288">
@@ -31156,12 +30834,12 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Other exploration costs</t>
+          <t>Part XII.6 tax related to flow-through shares</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -31171,47 +30849,51 @@
         </is>
       </c>
       <c r="F288" s="5" t="n">
-        <v>0.054739</v>
+        <v>0.002471</v>
       </c>
       <c r="G288" s="5" t="n">
-        <v>0.07537199999999999</v>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I288" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J288" s="5" t="n">
-        <v>0.020588</v>
-      </c>
-      <c r="K288" s="5" t="n">
-        <v>0.001793</v>
+        <v>0.004081</v>
+      </c>
+      <c r="H288" s="5" t="n">
+        <v>0.000673</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>0.000784</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L288" s="5" t="n">
-        <v>0.001683</v>
-      </c>
-      <c r="M288" s="5" t="n">
-        <v>0.005013</v>
-      </c>
-      <c r="N288" s="5" t="n">
-        <v>0.021003</v>
+        <v>0.006531</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O288" s="5" t="n">
-        <v>0.055406</v>
+        <v>0.020209</v>
       </c>
       <c r="P288" s="5" t="n">
-        <v>0.007355</v>
+        <v>0.006215</v>
       </c>
       <c r="Q288" s="5" t="n">
-        <v>0.002176</v>
+        <v>0.044863</v>
       </c>
       <c r="R288" s="5" t="n">
-        <v>0.011029</v>
+        <v>0.012944</v>
       </c>
     </row>
     <row r="289">
@@ -31222,80 +30904,62 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Financial expenses (note 13)</t>
-        </is>
-      </c>
-      <c r="D289" t="inlineStr"/>
+          <t>Administrative expenses total</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P289" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F289" s="5" t="n">
+        <v>1.189871</v>
+      </c>
+      <c r="G289" s="5" t="n">
+        <v>1.102966</v>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>0.867586</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>0.803491</v>
+      </c>
+      <c r="J289" s="5" t="n">
+        <v>0.861418</v>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>1.421323</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>1.566859</v>
+      </c>
+      <c r="M289" s="5" t="n">
+        <v>1.194335</v>
+      </c>
+      <c r="N289" s="5" t="n">
+        <v>1.401986</v>
+      </c>
+      <c r="O289" s="5" t="n">
+        <v>1.505011</v>
+      </c>
+      <c r="P289" s="5" t="n">
+        <v>1.713301</v>
       </c>
       <c r="Q289" s="5" t="n">
-        <v>0.006322</v>
+        <v>1.452986</v>
       </c>
       <c r="R289" s="5" t="n">
-        <v>0.043098</v>
+        <v>2.167377</v>
       </c>
     </row>
     <row r="290">
@@ -31311,24 +30975,24 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Sale of property option (note 9 (a) (b) (c) (d))</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F290" s="5" t="n">
-        <v>-0.035725</v>
-      </c>
-      <c r="G290" s="5" t="n">
-        <v>-0.026812</v>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -31340,32 +31004,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J290" s="5" t="n">
-        <v>-0.007820000000000001</v>
-      </c>
-      <c r="K290" s="5" t="n">
-        <v>-0.09914100000000001</v>
-      </c>
-      <c r="L290" s="5" t="n">
-        <v>-0.164374</v>
-      </c>
-      <c r="M290" s="5" t="n">
-        <v>-0.112325</v>
-      </c>
-      <c r="N290" s="5" t="n">
-        <v>-0.038575</v>
-      </c>
-      <c r="O290" s="5" t="n">
-        <v>-0.10954</v>
-      </c>
-      <c r="P290" s="5" t="n">
-        <v>-0.140583</v>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q290" s="5" t="n">
-        <v>-0.099064</v>
+        <v>-0.028</v>
       </c>
       <c r="R290" s="5" t="n">
-        <v>-0.162395</v>
+        <v>-0.25775</v>
       </c>
     </row>
     <row r="291">
@@ -31381,7 +31059,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Loss before deferred income and mining taxes</t>
+          <t>Write-down of mining assets and deferred exploration costs (note 9)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -31415,29 +31093,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K291" s="5" t="n">
-        <v>-1.81837</v>
-      </c>
-      <c r="L291" s="5" t="n">
-        <v>-6.828448</v>
-      </c>
-      <c r="M291" s="5" t="n">
-        <v>-1.087023</v>
-      </c>
-      <c r="N291" s="5" t="n">
-        <v>-1.350626</v>
-      </c>
-      <c r="O291" s="5" t="n">
-        <v>-1.452179</v>
-      </c>
-      <c r="P291" s="5" t="n">
-        <v>-1.493376</v>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q291" s="5" t="n">
-        <v>-11.255831</v>
+        <v>9.921411000000001</v>
       </c>
       <c r="R291" s="5" t="n">
-        <v>-5.189413</v>
+        <v>3.388054</v>
       </c>
     </row>
     <row r="292">
@@ -31453,7 +31143,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 16)</t>
+          <t>Other exploration costs</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -31462,66 +31152,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P292" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F292" s="5" t="n">
+        <v>0.054739</v>
+      </c>
+      <c r="G292" s="5" t="n">
+        <v>0.07537199999999999</v>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>0.001854</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>0.031214</v>
+      </c>
+      <c r="J292" s="5" t="n">
+        <v>0.020588</v>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>0.001793</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>0.001683</v>
+      </c>
+      <c r="M292" s="5" t="n">
+        <v>0.005013</v>
+      </c>
+      <c r="N292" s="5" t="n">
+        <v>0.021003</v>
+      </c>
+      <c r="O292" s="5" t="n">
+        <v>0.055406</v>
+      </c>
+      <c r="P292" s="5" t="n">
+        <v>0.007355</v>
       </c>
       <c r="Q292" s="5" t="n">
-        <v>-1.114117</v>
+        <v>0.002176</v>
       </c>
       <c r="R292" s="5" t="n">
-        <v>-0.850359</v>
+        <v>0.011029</v>
       </c>
     </row>
     <row r="293">
@@ -31537,14 +31205,10 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Net loss for the year attributable to shareholders</t>
-        </is>
-      </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Financial expenses (note 13)</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -31570,17 +31234,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J293" s="5" t="n">
-        <v>-0.692613</v>
-      </c>
-      <c r="K293" s="5" t="n">
-        <v>-1.866844</v>
-      </c>
-      <c r="L293" s="5" t="n">
-        <v>-4.989092</v>
-      </c>
-      <c r="M293" s="5" t="n">
-        <v>-0.984863</v>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
@@ -31592,14 +31264,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P293" s="5" t="n">
-        <v>-1.387911</v>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q293" s="5" t="n">
-        <v>-10.141714</v>
+        <v>0.006322</v>
       </c>
       <c r="R293" s="5" t="n">
-        <v>-4.339054</v>
+        <v>0.043098</v>
       </c>
     </row>
     <row r="294">
@@ -31615,73 +31289,57 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Change in fair value of other short-term financial assets (note 5)</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O294" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F294" s="5" t="n">
+        <v>-0.035725</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>-0.026812</v>
+      </c>
+      <c r="H294" s="5" t="n">
+        <v>-0.014317</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>-0.008411</v>
+      </c>
+      <c r="J294" s="5" t="n">
+        <v>-0.007820000000000001</v>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>-0.09914100000000001</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>-0.164374</v>
+      </c>
+      <c r="M294" s="5" t="n">
+        <v>-0.112325</v>
+      </c>
+      <c r="N294" s="5" t="n">
+        <v>-0.038575</v>
+      </c>
+      <c r="O294" s="5" t="n">
+        <v>-0.10954</v>
       </c>
       <c r="P294" s="5" t="n">
-        <v>-0.1526</v>
+        <v>-0.140583</v>
       </c>
       <c r="Q294" s="5" t="n">
-        <v>0.0064</v>
+        <v>-0.099064</v>
       </c>
       <c r="R294" s="5" t="n">
-        <v>0.08522399999999999</v>
+        <v>-0.162395</v>
       </c>
     </row>
     <row r="295">
@@ -31697,14 +31355,10 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year attributable to shareholders</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loss before deferred income and mining taxes</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -31735,35 +31389,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M295" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K295" s="5" t="n">
+        <v>-1.81837</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>-6.828448</v>
+      </c>
+      <c r="M295" s="5" t="n">
+        <v>-1.087023</v>
       </c>
       <c r="N295" s="5" t="n">
-        <v>-0.342945</v>
+        <v>-1.350626</v>
       </c>
       <c r="O295" s="5" t="n">
-        <v>-1.114138</v>
+        <v>-1.452179</v>
       </c>
       <c r="P295" s="5" t="n">
-        <v>-1.540511</v>
+        <v>-1.493376</v>
       </c>
       <c r="Q295" s="5" t="n">
-        <v>-10.135314</v>
+        <v>-11.255831</v>
       </c>
       <c r="R295" s="5" t="n">
-        <v>-4.25383</v>
+        <v>-5.189413</v>
       </c>
     </row>
     <row r="296">
@@ -31774,19 +31422,15 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Loss per share basic and diluted</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Deferred income and mining taxes (note 16)</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -31817,29 +31461,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K296" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="L296" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="M296" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N296" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O296" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P296" s="5" t="n">
-        <v>0</v>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q296" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-1.114117</v>
       </c>
       <c r="R296" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.850359</v>
       </c>
     </row>
     <row r="297">
@@ -31850,15 +31506,19 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic and diluted</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Net loss for the year attributable to shareholders</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -31874,46 +31534,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H297" s="5" t="n">
+        <v>-1.427049</v>
+      </c>
+      <c r="I297" s="5" t="n">
+        <v>-2.037757</v>
+      </c>
+      <c r="J297" s="5" t="n">
+        <v>-0.692613</v>
       </c>
       <c r="K297" s="5" t="n">
-        <v>144.53339</v>
+        <v>-1.866844</v>
       </c>
       <c r="L297" s="5" t="n">
-        <v>177.041733</v>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N297" s="5" t="n">
-        <v>217.420126</v>
-      </c>
-      <c r="O297" s="5" t="n">
-        <v>267.48902</v>
+        <v>-4.989092</v>
+      </c>
+      <c r="M297" s="5" t="n">
+        <v>-0.984863</v>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P297" s="5" t="n">
-        <v>323.64637</v>
+        <v>-1.387911</v>
       </c>
       <c r="Q297" s="5" t="n">
-        <v>354.519268</v>
+        <v>-10.141714</v>
       </c>
       <c r="R297" s="5" t="n">
-        <v>418.331881</v>
+        <v>-4.339054</v>
       </c>
     </row>
     <row r="298">
@@ -31924,12 +31580,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Salaries (note 11)</t>
+          <t>Change in fair value of other short-term financial assets (note 5)</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -31989,15 +31645,13 @@
         </is>
       </c>
       <c r="P298" s="5" t="n">
-        <v>0.552478</v>
+        <v>-0.1526</v>
       </c>
       <c r="Q298" s="5" t="n">
-        <v>0.5825939999999999</v>
-      </c>
-      <c r="R298" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0064</v>
+      </c>
+      <c r="R298" s="5" t="n">
+        <v>0.08522399999999999</v>
       </c>
     </row>
     <row r="299">
@@ -32008,15 +31662,19 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Share-based payments (note 10)</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Comprehensive loss for the year attributable to shareholders</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -32062,26 +31720,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N299" s="5" t="n">
+        <v>-0.342945</v>
+      </c>
+      <c r="O299" s="5" t="n">
+        <v>-1.114138</v>
       </c>
       <c r="P299" s="5" t="n">
-        <v>0.227252</v>
+        <v>-1.540511</v>
       </c>
       <c r="Q299" s="5" t="n">
-        <v>0.287999</v>
-      </c>
-      <c r="R299" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.135314</v>
+      </c>
+      <c r="R299" s="5" t="n">
+        <v>-4.25383</v>
       </c>
     </row>
     <row r="300">
@@ -32092,15 +31744,19 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Loss per share</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Sale of property option (note 8 (a))</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Loss per share basic and diluted</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -32131,41 +31787,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K300" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="M300" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="P300" s="5" t="n">
-        <v>-0.094</v>
+        <v>0</v>
       </c>
       <c r="Q300" s="5" t="n">
-        <v>-0.028</v>
-      </c>
-      <c r="R300" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="R300" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="301">
@@ -32176,12 +31820,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Write-down of mining assets and deferred exploration costs (note 8)</t>
+          <t>Weighted average number of common shares outstanding basic and diluted</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -32215,43 +31859,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K301" s="5" t="n">
+        <v>144.53339</v>
+      </c>
+      <c r="L301" s="5" t="n">
+        <v>177.041733</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N301" s="5" t="n">
+        <v>217.420126</v>
+      </c>
+      <c r="O301" s="5" t="n">
+        <v>267.48902</v>
+      </c>
+      <c r="P301" s="5" t="n">
+        <v>323.64637</v>
       </c>
       <c r="Q301" s="5" t="n">
-        <v>9.921411000000001</v>
-      </c>
-      <c r="R301" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>354.519268</v>
+      </c>
+      <c r="R301" s="5" t="n">
+        <v>418.331881</v>
       </c>
     </row>
     <row r="302">
@@ -32262,12 +31894,12 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Financial expenses (note 12)</t>
+          <t>Salaries (note 11)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -32327,10 +31959,10 @@
         </is>
       </c>
       <c r="P302" s="5" t="n">
-        <v>0.007303</v>
+        <v>0.552478</v>
       </c>
       <c r="Q302" s="5" t="n">
-        <v>0.006322</v>
+        <v>0.5825939999999999</v>
       </c>
       <c r="R302" t="inlineStr">
         <is>
@@ -32346,12 +31978,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 15)</t>
+          <t>Share-based payments (note 10)</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -32411,10 +32043,10 @@
         </is>
       </c>
       <c r="P303" s="5" t="n">
-        <v>-0.105465</v>
+        <v>0.227252</v>
       </c>
       <c r="Q303" s="5" t="n">
-        <v>-1.114117</v>
+        <v>0.287999</v>
       </c>
       <c r="R303" t="inlineStr">
         <is>
@@ -32430,12 +32062,12 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Salaries</t>
+          <t>Sale of property option (note 8 (a))</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -32444,11 +32076,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F304" s="5" t="n">
-        <v>0.31597</v>
-      </c>
-      <c r="G304" s="5" t="n">
-        <v>0.28888</v>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -32460,31 +32096,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J304" s="5" t="n">
-        <v>0.363306</v>
-      </c>
-      <c r="K304" s="5" t="n">
-        <v>0.326548</v>
-      </c>
-      <c r="L304" s="5" t="n">
-        <v>0.371638</v>
-      </c>
-      <c r="M304" s="5" t="n">
-        <v>0.369991</v>
-      </c>
-      <c r="N304" s="5" t="n">
-        <v>0.449456</v>
-      </c>
-      <c r="O304" s="5" t="n">
-        <v>0.536426</v>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P304" s="5" t="n">
-        <v>0.552478</v>
-      </c>
-      <c r="Q304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.094</v>
+      </c>
+      <c r="Q304" s="5" t="n">
+        <v>-0.028</v>
       </c>
       <c r="R304" t="inlineStr">
         <is>
@@ -32500,12 +32146,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Share-based payments-employees (note 12)</t>
+          <t>Write-down of mining assets and deferred exploration costs (note 8)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -32554,19 +32200,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N305" s="5" t="n">
-        <v>0.414079</v>
-      </c>
-      <c r="O305" s="5" t="n">
-        <v>0.172911</v>
-      </c>
-      <c r="P305" s="5" t="n">
-        <v>0.225962</v>
-      </c>
-      <c r="Q305" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q305" s="5" t="n">
+        <v>9.921411000000001</v>
       </c>
       <c r="R305" t="inlineStr">
         <is>
@@ -32582,12 +32232,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Share-based payments-consultants (note 12)</t>
+          <t>Financial expenses (note 12)</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -32636,19 +32286,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N306" s="5" t="n">
-        <v>0.027495</v>
-      </c>
-      <c r="O306" s="5" t="n">
-        <v>0.013757</v>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P306" s="5" t="n">
-        <v>0.00129</v>
-      </c>
-      <c r="Q306" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007303</v>
+      </c>
+      <c r="Q306" s="5" t="n">
+        <v>0.006322</v>
       </c>
       <c r="R306" t="inlineStr">
         <is>
@@ -32664,12 +32316,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Information to shareholder</t>
+          <t>Deferred income and mining taxes (note 15)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
@@ -32698,31 +32350,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J307" s="5" t="n">
-        <v>0.035518</v>
-      </c>
-      <c r="K307" s="5" t="n">
-        <v>0.050174</v>
-      </c>
-      <c r="L307" s="5" t="n">
-        <v>0.054641</v>
-      </c>
-      <c r="M307" s="5" t="n">
-        <v>0.042679</v>
-      </c>
-      <c r="N307" s="5" t="n">
-        <v>0.039779</v>
-      </c>
-      <c r="O307" s="5" t="n">
-        <v>0.039686</v>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P307" s="5" t="n">
-        <v>0.040485</v>
-      </c>
-      <c r="Q307" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.105465</v>
+      </c>
+      <c r="Q307" s="5" t="n">
+        <v>-1.114117</v>
       </c>
       <c r="R307" t="inlineStr">
         <is>
@@ -32738,12 +32400,12 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Sale of a written-off property option (note 9 (a))</t>
+          <t>Salaries</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -32752,54 +32414,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F308" s="5" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="G308" s="5" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.330678</v>
+      </c>
+      <c r="I308" s="5" t="n">
+        <v>0.383661</v>
+      </c>
+      <c r="J308" s="5" t="n">
+        <v>0.363306</v>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>0.326548</v>
+      </c>
+      <c r="L308" s="5" t="n">
+        <v>0.371638</v>
+      </c>
+      <c r="M308" s="5" t="n">
+        <v>0.369991</v>
       </c>
       <c r="N308" s="5" t="n">
-        <v>-0.052</v>
+        <v>0.449456</v>
       </c>
       <c r="O308" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.536426</v>
       </c>
       <c r="P308" s="5" t="n">
-        <v>-0.094</v>
+        <v>0.552478</v>
       </c>
       <c r="Q308" t="inlineStr">
         <is>
@@ -32820,12 +32466,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Financial expenses (note 14)</t>
+          <t>Share-based payments-employees (note 12)</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -32875,13 +32521,13 @@
         </is>
       </c>
       <c r="N309" s="5" t="n">
-        <v>0.018212</v>
+        <v>0.414079</v>
       </c>
       <c r="O309" s="5" t="n">
-        <v>0.012302</v>
+        <v>0.172911</v>
       </c>
       <c r="P309" s="5" t="n">
-        <v>0.007303</v>
+        <v>0.225962</v>
       </c>
       <c r="Q309" t="inlineStr">
         <is>
@@ -32902,12 +32548,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 17)</t>
+          <t>Share-based payments-consultants (note 12)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -32957,13 +32603,13 @@
         </is>
       </c>
       <c r="N310" s="5" t="n">
-        <v>-1.060181</v>
+        <v>0.027495</v>
       </c>
       <c r="O310" s="5" t="n">
-        <v>-0.398458</v>
+        <v>0.013757</v>
       </c>
       <c r="P310" s="5" t="n">
-        <v>-0.105465</v>
+        <v>0.00129</v>
       </c>
       <c r="Q310" t="inlineStr">
         <is>
@@ -32984,12 +32630,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Net loss for the period attributable to shareholders</t>
+          <t>Information to shareholder</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -33018,34 +32664,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M311" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J311" s="5" t="n">
+        <v>0.035518</v>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>0.050174</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>0.054641</v>
+      </c>
+      <c r="M311" s="5" t="n">
+        <v>0.042679</v>
       </c>
       <c r="N311" s="5" t="n">
-        <v>-0.290445</v>
+        <v>0.039779</v>
       </c>
       <c r="O311" s="5" t="n">
-        <v>-1.053721</v>
+        <v>0.039686</v>
       </c>
       <c r="P311" s="5" t="n">
-        <v>-1.387911</v>
+        <v>0.040485</v>
       </c>
       <c r="Q311" t="inlineStr">
         <is>
@@ -33071,7 +32709,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Change in fair value of other short-term financial assets</t>
+          <t>Sale of a written-off property option (note 9 (a))</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -33110,20 +32748,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L312" s="5" t="n">
-        <v>-0.00395</v>
-      </c>
-      <c r="M312" s="5" t="n">
-        <v>0.0009879999999999999</v>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N312" s="5" t="n">
-        <v>-0.0525</v>
+        <v>-0.052</v>
       </c>
       <c r="O312" s="5" t="n">
-        <v>-0.0822</v>
+        <v>-0.011</v>
       </c>
       <c r="P312" s="5" t="n">
-        <v>-0.1526</v>
+        <v>-0.094</v>
       </c>
       <c r="Q312" t="inlineStr">
         <is>
@@ -33149,14 +32791,10 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Deferred income taxes</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Financial expenses (note 14)</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -33202,18 +32840,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N313" s="5" t="n">
+        <v>0.018212</v>
       </c>
       <c r="O313" s="5" t="n">
-        <v>0.021783</v>
-      </c>
-      <c r="P313" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012302</v>
+      </c>
+      <c r="P313" s="5" t="n">
+        <v>0.007303</v>
       </c>
       <c r="Q313" t="inlineStr">
         <is>
@@ -33234,12 +32868,12 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Share-based payments-employees (note 9 and 10)</t>
+          <t>Deferred income and mining taxes (note 17)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -33278,26 +32912,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L314" s="5" t="n">
-        <v>0.393932</v>
-      </c>
-      <c r="M314" s="5" t="n">
-        <v>0.229001</v>
-      </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" s="5" t="n">
+        <v>-1.060181</v>
+      </c>
+      <c r="O314" s="5" t="n">
+        <v>-0.398458</v>
+      </c>
+      <c r="P314" s="5" t="n">
+        <v>-0.105465</v>
       </c>
       <c r="Q314" t="inlineStr">
         <is>
@@ -33318,12 +32950,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Share-based payments-consultants (note 9)</t>
+          <t>Net loss for the period attributable to shareholders</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -33362,26 +32994,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L315" s="5" t="n">
-        <v>0.006281</v>
-      </c>
-      <c r="M315" s="5" t="n">
-        <v>0.006788</v>
-      </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" s="5" t="n">
+        <v>-0.290445</v>
+      </c>
+      <c r="O315" s="5" t="n">
+        <v>-1.053721</v>
+      </c>
+      <c r="P315" s="5" t="n">
+        <v>-1.387911</v>
       </c>
       <c r="Q315" t="inlineStr">
         <is>
@@ -33402,29 +33032,29 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Change in fair value of other short-term financial assets</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F316" s="5" t="n">
-        <v>0.023432</v>
-      </c>
-      <c r="G316" s="5" t="n">
-        <v>0.026307</v>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -33436,34 +33066,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J316" s="5" t="n">
-        <v>0.016221</v>
-      </c>
-      <c r="K316" s="5" t="n">
-        <v>0.010028</v>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L316" s="5" t="n">
-        <v>0.01011</v>
-      </c>
-      <c r="M316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00395</v>
+      </c>
+      <c r="M316" s="5" t="n">
+        <v>0.0009879999999999999</v>
+      </c>
+      <c r="N316" s="5" t="n">
+        <v>-0.0525</v>
+      </c>
+      <c r="O316" s="5" t="n">
+        <v>-0.0822</v>
+      </c>
+      <c r="P316" s="5" t="n">
+        <v>-0.1526</v>
       </c>
       <c r="Q316" t="inlineStr">
         <is>
@@ -33484,15 +33110,19 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Fiancial expenses (note 11)</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr"/>
+          <t>Deferred income taxes</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -33528,21 +33158,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L317" s="5" t="n">
-        <v>0.018049</v>
-      </c>
-      <c r="M317" s="5" t="n">
-        <v>0.011998</v>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O317" s="5" t="n">
+        <v>0.021783</v>
       </c>
       <c r="P317" t="inlineStr">
         <is>
@@ -33568,12 +33200,12 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>(note 7)</t>
+          <t>Share-based payments-employees (note 9 and 10)</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
@@ -33613,12 +33245,10 @@
         </is>
       </c>
       <c r="L318" s="5" t="n">
-        <v>5.42428</v>
-      </c>
-      <c r="M318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.393932</v>
+      </c>
+      <c r="M318" s="5" t="n">
+        <v>0.229001</v>
       </c>
       <c r="N318" t="inlineStr">
         <is>
@@ -33654,12 +33284,12 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 14)</t>
+          <t>Share-based payments-consultants (note 9)</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -33699,10 +33329,10 @@
         </is>
       </c>
       <c r="L319" s="5" t="n">
-        <v>-1.839356</v>
+        <v>0.006281</v>
       </c>
       <c r="M319" s="5" t="n">
-        <v>-0.10216</v>
+        <v>0.006788</v>
       </c>
       <c r="N319" t="inlineStr">
         <is>
@@ -33738,55 +33368,49 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the period attributable to shareholders</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr"/>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E320" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F320" s="5" t="n">
+        <v>0.023432</v>
+      </c>
+      <c r="G320" s="5" t="n">
+        <v>0.026307</v>
+      </c>
+      <c r="H320" s="5" t="n">
+        <v>0.024001</v>
+      </c>
+      <c r="I320" s="5" t="n">
+        <v>0.021328</v>
+      </c>
+      <c r="J320" s="5" t="n">
+        <v>0.016221</v>
+      </c>
+      <c r="K320" s="5" t="n">
+        <v>0.010028</v>
       </c>
       <c r="L320" s="5" t="n">
-        <v>-4.993042</v>
-      </c>
-      <c r="M320" s="5" t="n">
-        <v>-0.9838750000000001</v>
+        <v>0.01011</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N320" t="inlineStr">
         <is>
@@ -33822,19 +33446,15 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding basic</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>BasicAverageShares</t>
-        </is>
-      </c>
+          <t>Fiancial expenses (note 11)</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -33871,10 +33491,10 @@
         </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>177.041733</v>
+        <v>0.018049</v>
       </c>
       <c r="M321" s="5" t="n">
-        <v>179.441539</v>
+        <v>0.011998</v>
       </c>
       <c r="N321" t="inlineStr">
         <is>
@@ -33910,19 +33530,15 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>diluted</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>(note 7)</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -33959,10 +33575,12 @@
         </is>
       </c>
       <c r="L322" s="5" t="n">
-        <v>178.609242</v>
-      </c>
-      <c r="M322" s="5" t="n">
-        <v>180.531336</v>
+        <v>5.42428</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N322" t="inlineStr">
         <is>
@@ -33998,12 +33616,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Share-based payments-employees (note 7 and 8)</t>
+          <t>Deferred income and mining taxes (note 14)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -34037,16 +33655,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K323" s="5" t="n">
-        <v>0.412666</v>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L323" s="5" t="n">
-        <v>0.393932</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.839356</v>
+      </c>
+      <c r="M323" s="5" t="n">
+        <v>-0.10216</v>
       </c>
       <c r="N323" t="inlineStr">
         <is>
@@ -34082,12 +33700,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Share-based payments-consultants (note 7)</t>
+          <t>Comprehensive loss for the period attributable to shareholders</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -34121,16 +33739,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K324" s="5" t="n">
-        <v>0.0709</v>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L324" s="5" t="n">
-        <v>0.006281</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.993042</v>
+      </c>
+      <c r="M324" s="5" t="n">
+        <v>-0.9838750000000001</v>
       </c>
       <c r="N324" t="inlineStr">
         <is>
@@ -34166,25 +33784,33 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Business development</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding basic</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F325" s="5" t="n">
-        <v>0.160827</v>
-      </c>
-      <c r="G325" s="5" t="n">
-        <v>0.172332</v>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -34196,19 +33822,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J325" s="5" t="n">
-        <v>0.103857</v>
-      </c>
-      <c r="K325" s="5" t="n">
-        <v>0.343478</v>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L325" s="5" t="n">
-        <v>0.518473</v>
-      </c>
-      <c r="M325" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>177.041733</v>
+      </c>
+      <c r="M325" s="5" t="n">
+        <v>179.441539</v>
       </c>
       <c r="N325" t="inlineStr">
         <is>
@@ -34244,17 +33872,17 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
+          <t>diluted</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>DilutedAverageShares</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -34262,11 +33890,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F326" s="5" t="n">
-        <v>0.002956</v>
-      </c>
-      <c r="G326" s="5" t="n">
-        <v>0.003334</v>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -34278,19 +33910,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J326" s="5" t="n">
-        <v>0.027087</v>
-      </c>
-      <c r="K326" s="5" t="n">
-        <v>0.022964</v>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L326" s="5" t="n">
-        <v>0.018049</v>
-      </c>
-      <c r="M326" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>178.609242</v>
+      </c>
+      <c r="M326" s="5" t="n">
+        <v>180.531336</v>
       </c>
       <c r="N326" t="inlineStr">
         <is>
@@ -34326,12 +33960,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>(note 6)</t>
+          <t>Share-based payments-employees (note 7 and 8)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -34366,10 +34000,10 @@
         </is>
       </c>
       <c r="K327" s="5" t="n">
-        <v>0.494395</v>
+        <v>0.412666</v>
       </c>
       <c r="L327" s="5" t="n">
-        <v>5.42428</v>
+        <v>0.393932</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
@@ -34410,12 +34044,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 11)</t>
+          <t>Share-based payments-consultants (note 7)</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -34450,10 +34084,10 @@
         </is>
       </c>
       <c r="K328" s="5" t="n">
-        <v>0.048474</v>
+        <v>0.0709</v>
       </c>
       <c r="L328" s="5" t="n">
-        <v>-1.839356</v>
+        <v>0.006281</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
@@ -34499,7 +34133,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Share-based payments-employees (note 10)</t>
+          <t>Business development</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -34508,36 +34142,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F329" s="5" t="n">
+        <v>0.160827</v>
+      </c>
+      <c r="G329" s="5" t="n">
+        <v>0.172332</v>
+      </c>
+      <c r="H329" s="5" t="n">
+        <v>0.067026</v>
+      </c>
+      <c r="I329" s="5" t="n">
+        <v>0.058348</v>
       </c>
       <c r="J329" s="5" t="n">
-        <v>0.125202</v>
+        <v>0.103857</v>
       </c>
       <c r="K329" s="5" t="n">
-        <v>0.412666</v>
-      </c>
-      <c r="L329" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.343478</v>
+      </c>
+      <c r="L329" s="5" t="n">
+        <v>0.518473</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
@@ -34583,45 +34207,39 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Share-based payments-consultants</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr"/>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F330" s="5" t="n">
+        <v>0.002956</v>
+      </c>
+      <c r="G330" s="5" t="n">
+        <v>0.003334</v>
+      </c>
+      <c r="H330" s="5" t="n">
+        <v>0.030199</v>
+      </c>
+      <c r="I330" s="5" t="n">
+        <v>0.001342</v>
       </c>
       <c r="J330" s="5" t="n">
-        <v>0.048499</v>
+        <v>0.027087</v>
       </c>
       <c r="K330" s="5" t="n">
-        <v>0.0709</v>
-      </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022964</v>
+      </c>
+      <c r="L330" s="5" t="n">
+        <v>0.018049</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
@@ -34667,7 +34285,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Write-off of exploration assets and deferred exploration costs</t>
+          <t>(note 6)</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -34704,10 +34322,8 @@
       <c r="K331" s="5" t="n">
         <v>0.494395</v>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L331" s="5" t="n">
+        <v>5.42428</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
@@ -34753,7 +34369,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Impairment of securities available-for-sale</t>
+          <t>Deferred income and mining taxes (note 11)</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -34787,15 +34403,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K332" s="5" t="n">
+        <v>0.048474</v>
+      </c>
+      <c r="L332" s="5" t="n">
+        <v>-1.839356</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
@@ -34836,12 +34448,12 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Gain on disposal of other short-term financial assets</t>
+          <t>Share-based payments-employees (note 10)</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -34871,12 +34483,10 @@
         </is>
       </c>
       <c r="J333" s="5" t="n">
-        <v>-0.08744300000000001</v>
-      </c>
-      <c r="K333" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.125202</v>
+      </c>
+      <c r="K333" s="5" t="n">
+        <v>0.412666</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -34922,12 +34532,12 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Gain on disposal of property, plant and equipment</t>
+          <t>Share-based payments-consultants</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -34957,12 +34567,10 @@
         </is>
       </c>
       <c r="J334" s="5" t="n">
-        <v>-0.000628</v>
-      </c>
-      <c r="K334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.048499</v>
+      </c>
+      <c r="K334" s="5" t="n">
+        <v>0.0709</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -35013,7 +34621,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Contractual services income</t>
+          <t>Write-off of exploration assets and deferred exploration costs</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -35042,13 +34650,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J335" s="5" t="n">
-        <v>-0.106</v>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K335" s="5" t="n">
+        <v>0.494395</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -35099,7 +34707,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>LOSS BEFORE DEFERRED INCOME AND MINING TAXES</t>
+          <t>Impairment of securities available-for-sale</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
@@ -35108,11 +34716,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F336" s="5" t="n">
-        <v>-1.586581</v>
-      </c>
-      <c r="G336" s="5" t="n">
-        <v>-2.109595</v>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
@@ -35124,11 +34736,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J336" s="5" t="n">
-        <v>-0.680115</v>
-      </c>
-      <c r="K336" s="5" t="n">
-        <v>-1.81837</v>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -35179,7 +34795,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Deferred income and mining taxes (note 13)</t>
+          <t>Gain on disposal of other short-term financial assets</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -35188,11 +34804,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F337" s="5" t="n">
-        <v>0.028037</v>
-      </c>
-      <c r="G337" s="5" t="n">
-        <v>0.019351</v>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
@@ -35205,10 +34825,12 @@
         </is>
       </c>
       <c r="J337" s="5" t="n">
-        <v>0.012498</v>
-      </c>
-      <c r="K337" s="5" t="n">
-        <v>0.048474</v>
+        <v>-0.08744300000000001</v>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -35254,29 +34876,29 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE basic</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on disposal of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr"/>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F338" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G338" s="5" t="n">
-        <v>-4e-08</v>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
@@ -35289,10 +34911,12 @@
         </is>
       </c>
       <c r="J338" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K338" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.000628</v>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -35338,45 +34962,43 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>diluted</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Contractual services income</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr"/>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F339" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G339" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="H339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H339" s="5" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>-0.104</v>
       </c>
       <c r="J339" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K339" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.106</v>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -35422,12 +35044,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>OUTSTANDING basic</t>
+          <t>LOSS BEFORE DEFERRED INCOME AND MINING TAXES</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -35437,26 +35059,22 @@
         </is>
       </c>
       <c r="F340" s="5" t="n">
-        <v>41.280451</v>
+        <v>-1.586581</v>
       </c>
       <c r="G340" s="5" t="n">
-        <v>50.850972</v>
-      </c>
-      <c r="H340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I340" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.109595</v>
+      </c>
+      <c r="H340" s="5" t="n">
+        <v>-1.664137</v>
+      </c>
+      <c r="I340" s="5" t="n">
+        <v>-2.669526</v>
       </c>
       <c r="J340" s="5" t="n">
-        <v>86.19305</v>
+        <v>-0.680115</v>
       </c>
       <c r="K340" s="5" t="n">
-        <v>144.53339</v>
+        <v>-1.81837</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -35502,12 +35120,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>diluted</t>
+          <t>Deferred income and mining taxes (note 13)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -35517,26 +35135,22 @@
         </is>
       </c>
       <c r="F341" s="5" t="n">
-        <v>41.867461</v>
+        <v>0.028037</v>
       </c>
       <c r="G341" s="5" t="n">
-        <v>50.888482</v>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.019351</v>
+      </c>
+      <c r="H341" s="5" t="n">
+        <v>-0.237088</v>
+      </c>
+      <c r="I341" s="5" t="n">
+        <v>-0.631769</v>
       </c>
       <c r="J341" s="5" t="n">
-        <v>86.19305</v>
+        <v>0.012498</v>
       </c>
       <c r="K341" s="5" t="n">
-        <v>144.53339</v>
+        <v>0.048474</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -35582,45 +35196,41 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>LOSS PER SHARE</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Share-based payments-employees</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>LOSS PER SHARE basic</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F342" s="5" t="n">
-        <v>0.236177</v>
+        <v>-4e-08</v>
       </c>
       <c r="G342" s="5" t="n">
-        <v>0.134823</v>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K342" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="H342" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I342" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J342" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K342" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -35666,45 +35276,41 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>LOSS PER SHARE</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Stationery and office expenses</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr"/>
+          <t>diluted</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F343" s="5" t="n">
-        <v>0.046947</v>
+        <v>-4e-08</v>
       </c>
       <c r="G343" s="5" t="n">
-        <v>0.032668</v>
-      </c>
-      <c r="H343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4e-08</v>
+      </c>
+      <c r="H343" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I343" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="J343" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K343" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -35750,12 +35356,12 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>OUTSTANDING</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Advertising</t>
+          <t>OUTSTANDING basic</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
@@ -35765,30 +35371,22 @@
         </is>
       </c>
       <c r="F344" s="5" t="n">
-        <v>0.040208</v>
+        <v>41.280451</v>
       </c>
       <c r="G344" s="5" t="n">
-        <v>0.036017</v>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K344" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50.850972</v>
+      </c>
+      <c r="H344" s="5" t="n">
+        <v>67.18177</v>
+      </c>
+      <c r="I344" s="5" t="n">
+        <v>76.265247</v>
+      </c>
+      <c r="J344" s="5" t="n">
+        <v>86.19305</v>
+      </c>
+      <c r="K344" s="5" t="n">
+        <v>144.53339</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -35834,12 +35432,12 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Administrative expenses</t>
+          <t>OUTSTANDING</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Shareholder's information</t>
+          <t>diluted</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -35849,30 +35447,22 @@
         </is>
       </c>
       <c r="F345" s="5" t="n">
-        <v>0.044858</v>
+        <v>41.867461</v>
       </c>
       <c r="G345" s="5" t="n">
-        <v>0.063553</v>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50.888482</v>
+      </c>
+      <c r="H345" s="5" t="n">
+        <v>67.18177</v>
+      </c>
+      <c r="I345" s="5" t="n">
+        <v>76.265247</v>
+      </c>
+      <c r="J345" s="5" t="n">
+        <v>86.19305</v>
+      </c>
+      <c r="K345" s="5" t="n">
+        <v>144.53339</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -35918,12 +35508,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Write-off of exploration assets and deferred exploration cost (note 8)</t>
+          <t>Share-based payments-employees (note 9)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -35932,21 +35522,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F346" s="5" t="n">
-        <v>0.389319</v>
-      </c>
-      <c r="G346" s="5" t="n">
-        <v>0.9580689999999999</v>
-      </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H346" s="5" t="n">
+        <v>0.097349</v>
+      </c>
+      <c r="I346" s="5" t="n">
+        <v>0.08643099999999999</v>
       </c>
       <c r="J346" t="inlineStr">
         <is>
@@ -36002,12 +35592,12 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Administrative expenses</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Management income</t>
+          <t>Shareholder's information</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -36017,22 +35607,16 @@
         </is>
       </c>
       <c r="F347" s="5" t="n">
-        <v>-0.011623</v>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I347" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.044858</v>
+      </c>
+      <c r="G347" s="5" t="n">
+        <v>0.063553</v>
+      </c>
+      <c r="H347" s="5" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="I347" s="5" t="n">
+        <v>0.032319</v>
       </c>
       <c r="J347" t="inlineStr">
         <is>
@@ -36093,76 +35677,668 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
+          <t>Write-off of deferred exploration costs</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H348" s="5" t="n">
+        <v>0.816845</v>
+      </c>
+      <c r="I348" s="5" t="n">
+        <v>1.871482</v>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Impairment of securities available-for-sale (note 18)</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H349" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I349" s="5" t="n">
+        <v>0.07575</v>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Management income</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F350" s="5" t="n">
+        <v>-0.011623</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H350" s="5" t="n">
+        <v>-0.017831</v>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Share-based payments-employees</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="n">
+        <v>0.236177</v>
+      </c>
+      <c r="G351" s="5" t="n">
+        <v>0.134823</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Stationery and office expenses</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F352" s="5" t="n">
+        <v>0.046947</v>
+      </c>
+      <c r="G352" s="5" t="n">
+        <v>0.032668</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Administrative expenses</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F353" s="5" t="n">
+        <v>0.040208</v>
+      </c>
+      <c r="G353" s="5" t="n">
+        <v>0.036017</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Write-off of exploration assets and deferred exploration cost (note 8)</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F354" s="5" t="n">
+        <v>0.389319</v>
+      </c>
+      <c r="G354" s="5" t="n">
+        <v>0.9580689999999999</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
           <t>NET LOSS FOR THE YEAR</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
+      <c r="D355" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F348" s="5" t="n">
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F355" s="5" t="n">
         <v>-1.614618</v>
       </c>
-      <c r="G348" s="5" t="n">
+      <c r="G355" s="5" t="n">
         <v>-2.128946</v>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R348" t="inlineStr">
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
         <is>
           <t>-</t>
         </is>
